--- a/erp-server/erp-server-oms/src/main/resources/excel/exhibitionOrderDetailTemplate.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/exhibitionOrderDetailTemplate.xlsx
@@ -1359,7 +1359,7 @@
     <col min="33" max="33" width="19.8166666666667" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33">
+    <row r="1" ht="14.25" spans="1:33">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
